--- a/基本設計/15_ユーザーと組織_DB基本設計書.xlsx
+++ b/基本設計/15_ユーザーと組織_DB基本設計書.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R7ca02454129440b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R83b8f51b119d4060"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_テーブル一覧" sheetId="23" r:id="Re4220dd9ad514ac9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_ER関係" sheetId="24" r:id="R93a7c6fadfa54239"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_論理項目定義" sheetId="25" r:id="Rf4c38ff5b10f4d65"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25_制約・索引" sheetId="26" r:id="Re26d093d336b4dea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="26_ステータス定義" sheetId="27" r:id="R53da74fa3fc24879"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Rc0a9785d640b40e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R754dcadef624401a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_テーブル一覧" sheetId="23" r:id="Rde5aac282bab4d27"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_ER関係" sheetId="24" r:id="R1ee4b02d56124e96"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_論理項目定義" sheetId="25" r:id="R72c714bd63864169"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25_制約・索引" sheetId="26" r:id="R6937042e34334850"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="26_ステータス定義" sheetId="27" r:id="Ra09bb267f4f7497a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1117,10 +1117,7 @@
       <x:c r="F16" s="145"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" t="str">
-        <x:v>本書は Company WorkHub の基本設計内容を定義する。
-Ver.1.8 は状態変更入口、API/DB制約、取込Transaction、日報一意制約、通知・Token保持を整合した再Review対応版である。</x:v>
-      </x:c>
+      <x:c r="A17"/>
       <x:c r="C17"/>
       <x:c r="D17"/>
       <x:c r="E17"/>
@@ -1135,25 +1132,22 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19"/>
-      <x:c r="B19" s="187" t="str">
-        <x:v>本書は Company WorkHub の基本設計内容を定義する。
-Ver.1.7 は状態変更入口、API/DB制約、取込Transaction、日報一意制約、通知・Token保持を整合した再Review対応版である。</x:v>
-      </x:c>
-      <x:c r="C19" s="187"/>
-      <x:c r="D19" s="187"/>
-      <x:c r="E19" s="187"/>
-      <x:c r="F19" s="187"/>
-      <x:c r="G19" s="187"/>
-      <x:c r="H19" s="187"/>
+      <x:c r="B19"/>
+      <x:c r="C19"/>
+      <x:c r="D19"/>
+      <x:c r="E19"/>
+      <x:c r="F19"/>
+      <x:c r="G19"/>
+      <x:c r="H19"/>
     </x:row>
     <x:row r="20">
-      <x:c r="B20" s="187"/>
-      <x:c r="C20" s="187"/>
-      <x:c r="D20" s="187"/>
-      <x:c r="E20" s="187"/>
-      <x:c r="F20" s="187"/>
-      <x:c r="G20" s="187"/>
-      <x:c r="H20" s="187"/>
+      <x:c r="B20"/>
+      <x:c r="C20"/>
+      <x:c r="D20"/>
+      <x:c r="E20"/>
+      <x:c r="F20"/>
+      <x:c r="G20"/>
+      <x:c r="H20"/>
     </x:row>
     <x:row r="21">
       <x:c r="B21" s="187"/>
